--- a/content/tutor/word-traps/함정단어.xlsx
+++ b/content/tutor/word-traps/함정단어.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1507,7 +1507,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>선생님: 필요 없음 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1540,7 +1549,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>선생님: 필요 없음 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1573,7 +1591,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>선생님: 필요 없음 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1606,7 +1633,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>선생님: 필요 없음 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1639,7 +1675,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>선생님: 필요 없음 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2563,7 +2608,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>선생님 확인 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2695,7 +2749,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>선생님 확인 (2026-10-16)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2762,7 +2825,6 @@
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2796,7 +2858,6 @@
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2830,7 +2891,6 @@
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2864,7 +2924,6 @@
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2898,7 +2957,6 @@
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2932,7 +2990,6 @@
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2966,7 +3023,6 @@
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3000,7 +3056,6 @@
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3034,7 +3089,6 @@
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3067,8 +3121,16 @@
           <t>중·초</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3102,7 +3164,6 @@
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3135,8 +3196,16 @@
           <t>초</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3170,7 +3239,6 @@
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3204,7 +3272,6 @@
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3238,7 +3305,6 @@
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3272,7 +3338,6 @@
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3306,7 +3371,6 @@
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3340,7 +3404,6 @@
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3374,7 +3437,6 @@
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3408,7 +3470,6 @@
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3442,7 +3503,6 @@
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3476,7 +3536,6 @@
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3510,7 +3569,762 @@
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>work</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>일하다</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>효과가 있다, 작동하다</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>appear to</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>나타나다</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>~처럼 보이다 (= seem to)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>manner</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>매너(예절)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>방식 (in this ~)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Once</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>한 번</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>일단 ~하면 (접속사)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>room</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>여지 (no need or room)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>that's all there is to it</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>그게 다다, 그저 그뿐이다</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>upon receiving</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>~을 받자마자</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>undone</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>undo(취소하다)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>무너진, 망가진 (undone by ~)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ones</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>하나들</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>앞 명사를 받음 — 여기서는 deliberations</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3월 36번</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>interpersonal</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>모양</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>대인 간의 (inter 사이 + personal)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>중·초</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>선생님 표시판 (2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2024년 3월 23번</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mortality</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>모양</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>morality(도덕성)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>죽음, 언젠가 죽는다는 것 (even our own mortality)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 요청 — morality와 헷갈림</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2024년 3월 23번</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>drive</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>운전하다</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>욕구, 충동 (an innate drive = 타고난 욕구)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 — 운전하다로만 앎</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2024년 3월 22번</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>driven</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>운전된</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>~에 이끌린, 좌우된 (emotionally driven decisions = 감정에 좌우된 결정)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 — drive를 운전하다로만 앎</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2024년 3월 23번</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>한 번</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>일단 ~하면 (접속사, once you can identify them = 일단 그들을 알아보게 되면)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 요청</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2024년 3월 23번</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>so much so that</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>(뜻을 모름)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>너무 그래서 ~할 정도로 (앞 내용이 얼마나 심한지)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 요청</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2024년 3월 23번</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>given</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>주어진</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>~이 주어지면, ~라면 (given a choice = 선택이 주어지면) · 비슷한 말: provided (~라면)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 요청 — 동의어 provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2024년 3월 24번</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>even if</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>쓰임</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>심지어 ~라면</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>비록 ~라도 (even if they live thousands of miles away = 수천 마일 떨어져 살더라도)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 요청</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2024년 3월 24번</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>뜻</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>마지막</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>지속되다, 오래가다 (will last for generations = 여러 세대 동안 지속될)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>고·중·초</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-18 선생님 — 뜻 상자에 마지막으로 잘못 나옴</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -3547,11 +4361,10 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 사용(O/X) 칸: 넣을 단어는 O, 뺄 단어는 X. 비워 두면 O로 봐요.</t>
+          <t>1. 사용(O/X) 칸: 넣을 단어는 O, 뺄 단어는 X. O인 단어만 수업에 💡 Tip으로 떠요. 비워 두면 아직 안 본 후보라 안 떠요.</t>
         </is>
       </c>
     </row>
@@ -3590,7 +4403,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -3604,9 +4416,6 @@
           <t>시험지 아래 *로 풀어 준 단어(inextricably, premise, pendulum, iteration 등)는 뺐어요.</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
